--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1934,6 +1934,792 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122459462</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56290</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>667920</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6612268</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122459424</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56292</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>667920</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6612268</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122459489</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56285</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>667920</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6612268</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122459482</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56288</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>667920</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6612268</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122459622</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56271</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>667920</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6612268</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122459555</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56278</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>667920</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612268</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459462</v>
+        <v>122459507</v>
       </c>
       <c r="B13" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,26 +1953,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>177</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2068,7 +2068,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459424</v>
+        <v>122459408</v>
       </c>
       <c r="B14" t="n">
         <v>56292</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459489</v>
+        <v>122459482</v>
       </c>
       <c r="B15" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,26 +2215,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459482</v>
+        <v>122459441</v>
       </c>
       <c r="B16" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,26 +2346,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2461,7 +2461,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459622</v>
+        <v>122459597</v>
       </c>
       <c r="B17" t="n">
         <v>56271</v>
@@ -2550,22 +2550,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459507</v>
+        <v>122459597</v>
       </c>
       <c r="B13" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,30 +1949,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459408</v>
+        <v>122459555</v>
       </c>
       <c r="B14" t="n">
-        <v>56292</v>
+        <v>56278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459441</v>
+        <v>122459424</v>
       </c>
       <c r="B16" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459597</v>
+        <v>122459441</v>
       </c>
       <c r="B17" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,30 +2473,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459555</v>
+        <v>122459489</v>
       </c>
       <c r="B18" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,26 +2608,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459597</v>
+        <v>122459489</v>
       </c>
       <c r="B13" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,30 +1949,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2061,17 +2056,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459555</v>
+        <v>122459622</v>
       </c>
       <c r="B14" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2075,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2147,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2182,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459482</v>
+        <v>122459462</v>
       </c>
       <c r="B15" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,26 +2205,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,22 +2273,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,17 +2308,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459424</v>
+        <v>122459555</v>
       </c>
       <c r="B16" t="n">
-        <v>56292</v>
+        <v>56278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,25 +2327,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206002</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Brunlångöra</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2419,22 +2399,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,17 +2434,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459441</v>
+        <v>122459424</v>
       </c>
       <c r="B17" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,30 +2453,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>206002</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2550,22 +2525,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,17 +2560,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459489</v>
+        <v>122459482</v>
       </c>
       <c r="B18" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,26 +2583,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459489</v>
+        <v>122459441</v>
       </c>
       <c r="B13" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1953,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2056,17 +2061,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459622</v>
+        <v>122459507</v>
       </c>
       <c r="B14" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,25 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>177</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2189,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459462</v>
+        <v>122459622</v>
       </c>
       <c r="B15" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,25 +2211,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2315,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459555</v>
+        <v>122459482</v>
       </c>
       <c r="B16" t="n">
-        <v>56278</v>
+        <v>56292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,16 +2346,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205992</v>
+        <v>100111</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2434,7 +2454,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2444,7 +2464,7 @@
         <v>122459424</v>
       </c>
       <c r="B17" t="n">
-        <v>56292</v>
+        <v>56296</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2459,6 +2479,11 @@
       <c r="E17" t="n">
         <v>206002</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Plecotus auritus</t>
@@ -2560,17 +2585,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Emily Macgregor, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459482</v>
+        <v>122459555</v>
       </c>
       <c r="B18" t="n">
-        <v>56288</v>
+        <v>56282</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,16 +2608,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100111</v>
+        <v>205992</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459441</v>
+        <v>122459489</v>
       </c>
       <c r="B13" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,26 +1953,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Alvunger, Jacqueline Nelms, Torge Gerwin</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459507</v>
+        <v>122459441</v>
       </c>
       <c r="B14" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,26 +2084,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,14 +2192,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459622</v>
+        <v>122459597</v>
       </c>
       <c r="B15" t="n">
         <v>56275</v>
@@ -2288,22 +2288,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459482</v>
+        <v>122459408</v>
       </c>
       <c r="B16" t="n">
-        <v>56292</v>
+        <v>56296</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100111</v>
+        <v>206002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459424</v>
+        <v>122459555</v>
       </c>
       <c r="B17" t="n">
-        <v>56296</v>
+        <v>56282</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emily Macgregor, Torge Gerwin</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459555</v>
+        <v>122459482</v>
       </c>
       <c r="B18" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459489</v>
+        <v>122459408</v>
       </c>
       <c r="B13" t="n">
-        <v>56289</v>
+        <v>56296</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,30 +1949,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459408</v>
+        <v>122459555</v>
       </c>
       <c r="B16" t="n">
-        <v>56296</v>
+        <v>56282</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459555</v>
+        <v>122459482</v>
       </c>
       <c r="B17" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,21 +2477,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459482</v>
+        <v>122459489</v>
       </c>
       <c r="B18" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,26 +2608,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,7 +1937,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459408</v>
+        <v>122459424</v>
       </c>
       <c r="B13" t="n">
         <v>56296</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459441</v>
+        <v>122459622</v>
       </c>
       <c r="B14" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459597</v>
+        <v>122459507</v>
       </c>
       <c r="B15" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,30 +2211,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>177</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459555</v>
+        <v>122459482</v>
       </c>
       <c r="B16" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459482</v>
+        <v>122459462</v>
       </c>
       <c r="B17" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,26 +2477,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459489</v>
+        <v>122459555</v>
       </c>
       <c r="B18" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,26 +2608,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459424</v>
+        <v>122459441</v>
       </c>
       <c r="B13" t="n">
-        <v>56296</v>
+        <v>56294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,30 +1949,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459622</v>
+        <v>122459489</v>
       </c>
       <c r="B14" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459507</v>
+        <v>122459482</v>
       </c>
       <c r="B15" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,26 +2215,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459482</v>
+        <v>122459408</v>
       </c>
       <c r="B16" t="n">
-        <v>56292</v>
+        <v>56296</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100111</v>
+        <v>206002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459462</v>
+        <v>122459597</v>
       </c>
       <c r="B17" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,30 +2473,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459441</v>
+        <v>122459462</v>
       </c>
       <c r="B13" t="n">
-        <v>56294</v>
+        <v>56295</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459489</v>
+        <v>122459424</v>
       </c>
       <c r="B14" t="n">
-        <v>56289</v>
+        <v>56297</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459482</v>
+        <v>122459622</v>
       </c>
       <c r="B15" t="n">
-        <v>56292</v>
+        <v>56276</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,30 +2211,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459408</v>
+        <v>122459489</v>
       </c>
       <c r="B16" t="n">
-        <v>56296</v>
+        <v>56290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459597</v>
+        <v>122459555</v>
       </c>
       <c r="B17" t="n">
-        <v>56275</v>
+        <v>56283</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,30 +2473,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459555</v>
+        <v>122459482</v>
       </c>
       <c r="B18" t="n">
-        <v>56282</v>
+        <v>56293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459462</v>
+        <v>122459424</v>
       </c>
       <c r="B13" t="n">
-        <v>56295</v>
+        <v>56297</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,30 +1949,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2068,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459424</v>
+        <v>122459597</v>
       </c>
       <c r="B14" t="n">
-        <v>56297</v>
+        <v>56276</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,26 +2084,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459622</v>
+        <v>122459482</v>
       </c>
       <c r="B15" t="n">
-        <v>56276</v>
+        <v>56293</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,30 +2211,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459555</v>
+        <v>122459462</v>
       </c>
       <c r="B17" t="n">
-        <v>56283</v>
+        <v>56295</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,26 +2477,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459482</v>
+        <v>122459555</v>
       </c>
       <c r="B18" t="n">
-        <v>56293</v>
+        <v>56283</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122459424</v>
+        <v>122459462</v>
       </c>
       <c r="B13" t="n">
-        <v>56297</v>
+        <v>56295</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,30 +1949,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2068,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459597</v>
+        <v>122459489</v>
       </c>
       <c r="B14" t="n">
-        <v>56276</v>
+        <v>56290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2199,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459482</v>
+        <v>122459408</v>
       </c>
       <c r="B15" t="n">
-        <v>56293</v>
+        <v>56297</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,30 +2211,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100111</v>
+        <v>206002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459489</v>
+        <v>122459597</v>
       </c>
       <c r="B16" t="n">
-        <v>56290</v>
+        <v>56276</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459462</v>
+        <v>122459482</v>
       </c>
       <c r="B17" t="n">
-        <v>56295</v>
+        <v>56293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,26 +2477,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -2068,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459507</v>
+        <v>122459424</v>
       </c>
       <c r="B14" t="n">
-        <v>56384</v>
+        <v>56391</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2199,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459462</v>
+        <v>122459482</v>
       </c>
       <c r="B15" t="n">
-        <v>56389</v>
+        <v>56387</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,26 +2215,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459482</v>
+        <v>122459462</v>
       </c>
       <c r="B16" t="n">
-        <v>56387</v>
+        <v>56389</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,26 +2346,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459555</v>
+        <v>122459489</v>
       </c>
       <c r="B17" t="n">
-        <v>56377</v>
+        <v>56384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,26 +2477,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122459424</v>
+        <v>122459555</v>
       </c>
       <c r="B18" t="n">
-        <v>56391</v>
+        <v>56377</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2604,25 +2604,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2681,22 +2681,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 27425-2023 artfynd.xlsx
+++ b/artfynd/A 27425-2023 artfynd.xlsx
@@ -2068,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459424</v>
+        <v>122459489</v>
       </c>
       <c r="B14" t="n">
-        <v>56391</v>
+        <v>56384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459482</v>
+        <v>122459408</v>
       </c>
       <c r="B15" t="n">
-        <v>56387</v>
+        <v>56391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,30 +2211,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100111</v>
+        <v>206002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2330,7 +2330,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459462</v>
+        <v>122459441</v>
       </c>
       <c r="B16" t="n">
         <v>56389</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122459489</v>
+        <v>122459482</v>
       </c>
       <c r="B17" t="n">
-        <v>56384</v>
+        <v>56387</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,26 +2477,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
